--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120896402</v>
+        <v>120893848</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474978</v>
+        <v>474727</v>
       </c>
       <c r="R2" t="n">
-        <v>6670823</v>
+        <v>6670955</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120894059</v>
+        <v>120896402</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474698</v>
+        <v>474978</v>
       </c>
       <c r="R3" t="n">
-        <v>6671085</v>
+        <v>6670823</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120895528</v>
+        <v>120896288</v>
       </c>
       <c r="B4" t="n">
-        <v>95660</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +920,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474569</v>
+        <v>474950</v>
       </c>
       <c r="R4" t="n">
-        <v>6670992</v>
+        <v>6670755</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120896971</v>
+        <v>120894059</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,52 +1046,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474968</v>
+        <v>474698</v>
       </c>
       <c r="R5" t="n">
-        <v>6670949</v>
+        <v>6671085</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120893848</v>
+        <v>120893178</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>95660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,21 +1162,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474727</v>
+        <v>474738</v>
       </c>
       <c r="R6" t="n">
-        <v>6670955</v>
+        <v>6670733</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120893178</v>
+        <v>120895528</v>
       </c>
       <c r="B7" t="n">
         <v>95660</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474738</v>
+        <v>474569</v>
       </c>
       <c r="R7" t="n">
-        <v>6670733</v>
+        <v>6670992</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120896288</v>
+        <v>120896971</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1405,29 +1405,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474950</v>
+        <v>474968</v>
       </c>
       <c r="R8" t="n">
-        <v>6670755</v>
+        <v>6670949</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120893848</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120896402</v>
+        <v>120896971</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,19 +827,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474978</v>
+        <v>474968</v>
       </c>
       <c r="R3" t="n">
-        <v>6670823</v>
+        <v>6670949</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120896288</v>
+        <v>120894059</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,52 +925,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474950</v>
+        <v>474698</v>
       </c>
       <c r="R4" t="n">
-        <v>6670755</v>
+        <v>6671085</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120894059</v>
+        <v>120896288</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,38 +1037,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474698</v>
+        <v>474950</v>
       </c>
       <c r="R5" t="n">
-        <v>6671085</v>
+        <v>6670755</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120893178</v>
+        <v>120896402</v>
       </c>
       <c r="B6" t="n">
-        <v>95660</v>
+        <v>92018</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,38 +1163,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474738</v>
+        <v>474978</v>
       </c>
       <c r="R6" t="n">
-        <v>6670733</v>
+        <v>6670823</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120895528</v>
+        <v>120893178</v>
       </c>
       <c r="B7" t="n">
-        <v>95660</v>
+        <v>95678</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474569</v>
+        <v>474738</v>
       </c>
       <c r="R7" t="n">
-        <v>6670992</v>
+        <v>6670733</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120896971</v>
+        <v>120895528</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>95678</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,52 +1396,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474968</v>
+        <v>474569</v>
       </c>
       <c r="R8" t="n">
-        <v>6670949</v>
+        <v>6670992</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120893848</v>
+        <v>120896288</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474727</v>
+        <v>474950</v>
       </c>
       <c r="R2" t="n">
-        <v>6670955</v>
+        <v>6670755</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120896971</v>
+        <v>120893848</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>78631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +813,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474968</v>
+        <v>474727</v>
       </c>
       <c r="R3" t="n">
-        <v>6670949</v>
+        <v>6670955</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120894059</v>
+        <v>120893178</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
+        <v>95680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474698</v>
+        <v>474738</v>
       </c>
       <c r="R4" t="n">
-        <v>6671085</v>
+        <v>6670733</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120896288</v>
+        <v>120895528</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>95680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,52 +1037,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474950</v>
+        <v>474569</v>
       </c>
       <c r="R5" t="n">
-        <v>6670755</v>
+        <v>6670992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1140,7 @@
         <v>120896402</v>
       </c>
       <c r="B6" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1272,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120893178</v>
+        <v>120896971</v>
       </c>
       <c r="B7" t="n">
-        <v>95678</v>
+        <v>98133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,38 +1270,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474738</v>
+        <v>474968</v>
       </c>
       <c r="R7" t="n">
-        <v>6670733</v>
+        <v>6670949</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120895528</v>
+        <v>120894059</v>
       </c>
       <c r="B8" t="n">
-        <v>95678</v>
+        <v>90744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474569</v>
+        <v>474698</v>
       </c>
       <c r="R8" t="n">
-        <v>6670992</v>
+        <v>6671085</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120896288</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120893848</v>
+        <v>120896402</v>
       </c>
       <c r="B3" t="n">
-        <v>78631</v>
+        <v>92021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,38 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474727</v>
+        <v>474978</v>
       </c>
       <c r="R3" t="n">
-        <v>6670955</v>
+        <v>6670823</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120893178</v>
+        <v>120894059</v>
       </c>
       <c r="B4" t="n">
-        <v>95680</v>
+        <v>90745</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474738</v>
+        <v>474698</v>
       </c>
       <c r="R4" t="n">
-        <v>6670733</v>
+        <v>6671085</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120895528</v>
+        <v>120893178</v>
       </c>
       <c r="B5" t="n">
-        <v>95680</v>
+        <v>95687</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474569</v>
+        <v>474738</v>
       </c>
       <c r="R5" t="n">
-        <v>6670992</v>
+        <v>6670733</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120896402</v>
+        <v>120893848</v>
       </c>
       <c r="B6" t="n">
-        <v>92020</v>
+        <v>78632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,47 +1158,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474978</v>
+        <v>474727</v>
       </c>
       <c r="R6" t="n">
-        <v>6670823</v>
+        <v>6670955</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
         <v>120896971</v>
       </c>
       <c r="B7" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120894059</v>
+        <v>120895528</v>
       </c>
       <c r="B8" t="n">
-        <v>90744</v>
+        <v>95687</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474698</v>
+        <v>474569</v>
       </c>
       <c r="R8" t="n">
-        <v>6671085</v>
+        <v>6670992</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120893848</v>
+        <v>120896971</v>
       </c>
       <c r="B6" t="n">
-        <v>78632</v>
+        <v>98140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,38 +1158,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474727</v>
+        <v>474968</v>
       </c>
       <c r="R6" t="n">
-        <v>6670955</v>
+        <v>6670949</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120896971</v>
+        <v>120893848</v>
       </c>
       <c r="B7" t="n">
-        <v>98140</v>
+        <v>78632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,52 +1284,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474968</v>
+        <v>474727</v>
       </c>
       <c r="R7" t="n">
-        <v>6670949</v>
+        <v>6670955</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120896971</v>
+        <v>120893848</v>
       </c>
       <c r="B6" t="n">
-        <v>98140</v>
+        <v>78632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,52 +1158,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474968</v>
+        <v>474727</v>
       </c>
       <c r="R6" t="n">
-        <v>6670949</v>
+        <v>6670955</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120893848</v>
+        <v>120896971</v>
       </c>
       <c r="B7" t="n">
-        <v>78632</v>
+        <v>98140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,38 +1270,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474727</v>
+        <v>474968</v>
       </c>
       <c r="R7" t="n">
-        <v>6670955</v>
+        <v>6670949</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120896288</v>
+        <v>120894059</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>90754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474950</v>
+        <v>474698</v>
       </c>
       <c r="R2" t="n">
-        <v>6670755</v>
+        <v>6671085</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120896402</v>
+        <v>120896971</v>
       </c>
       <c r="B3" t="n">
-        <v>92021</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,19 +827,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474978</v>
+        <v>474968</v>
       </c>
       <c r="R3" t="n">
-        <v>6670823</v>
+        <v>6670949</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120894059</v>
+        <v>120896402</v>
       </c>
       <c r="B4" t="n">
-        <v>90745</v>
+        <v>92030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,38 +925,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474698</v>
+        <v>474978</v>
       </c>
       <c r="R4" t="n">
-        <v>6671085</v>
+        <v>6670823</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120893178</v>
+        <v>120896288</v>
       </c>
       <c r="B5" t="n">
-        <v>95687</v>
+        <v>98149</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,38 +1046,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474738</v>
+        <v>474950</v>
       </c>
       <c r="R5" t="n">
-        <v>6670733</v>
+        <v>6670755</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1163,7 @@
         <v>120893848</v>
       </c>
       <c r="B6" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1258,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120896971</v>
+        <v>120895528</v>
       </c>
       <c r="B7" t="n">
-        <v>98140</v>
+        <v>95696</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,52 +1284,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474968</v>
+        <v>474569</v>
       </c>
       <c r="R7" t="n">
-        <v>6670949</v>
+        <v>6670992</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120895528</v>
+        <v>120893178</v>
       </c>
       <c r="B8" t="n">
-        <v>95687</v>
+        <v>95696</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474569</v>
+        <v>474738</v>
       </c>
       <c r="R8" t="n">
-        <v>6670992</v>
+        <v>6670733</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120894059</v>
+        <v>120893848</v>
       </c>
       <c r="B2" t="n">
-        <v>90754</v>
+        <v>78643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474698</v>
+        <v>474727</v>
       </c>
       <c r="R2" t="n">
-        <v>6671085</v>
+        <v>6670955</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120896971</v>
+        <v>120893178</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
+        <v>95704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474968</v>
+        <v>474738</v>
       </c>
       <c r="R3" t="n">
-        <v>6670949</v>
+        <v>6670733</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +902,7 @@
         <v>120896402</v>
       </c>
       <c r="B4" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1034,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120896288</v>
+        <v>120896971</v>
       </c>
       <c r="B5" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,29 +1055,29 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474950</v>
+        <v>474968</v>
       </c>
       <c r="R5" t="n">
-        <v>6670755</v>
+        <v>6670949</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120893848</v>
+        <v>120895528</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>95704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,21 +1162,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474727</v>
+        <v>474569</v>
       </c>
       <c r="R6" t="n">
-        <v>6670955</v>
+        <v>6670992</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120895528</v>
+        <v>120896288</v>
       </c>
       <c r="B7" t="n">
-        <v>95696</v>
+        <v>98157</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,38 +1270,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474569</v>
+        <v>474950</v>
       </c>
       <c r="R7" t="n">
-        <v>6670992</v>
+        <v>6670755</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120893178</v>
+        <v>120894059</v>
       </c>
       <c r="B8" t="n">
-        <v>95696</v>
+        <v>90761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474738</v>
+        <v>474698</v>
       </c>
       <c r="R8" t="n">
-        <v>6670733</v>
+        <v>6671085</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120896971</v>
+        <v>120895528</v>
       </c>
       <c r="B5" t="n">
-        <v>98157</v>
+        <v>95704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,52 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474968</v>
+        <v>474569</v>
       </c>
       <c r="R5" t="n">
-        <v>6670949</v>
+        <v>6670992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120895528</v>
+        <v>120896971</v>
       </c>
       <c r="B6" t="n">
-        <v>95704</v>
+        <v>98157</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,38 +1144,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474569</v>
+        <v>474968</v>
       </c>
       <c r="R6" t="n">
-        <v>6670992</v>
+        <v>6670949</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120895528</v>
+        <v>120896971</v>
       </c>
       <c r="B5" t="n">
-        <v>95704</v>
+        <v>98157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1032,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474569</v>
+        <v>474968</v>
       </c>
       <c r="R5" t="n">
-        <v>6670992</v>
+        <v>6670949</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120896971</v>
+        <v>120895528</v>
       </c>
       <c r="B6" t="n">
-        <v>98157</v>
+        <v>95704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,52 +1158,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474968</v>
+        <v>474569</v>
       </c>
       <c r="R6" t="n">
-        <v>6670949</v>
+        <v>6670992</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120893848</v>
+        <v>120895528</v>
       </c>
       <c r="B2" t="n">
-        <v>78643</v>
+        <v>95706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474727</v>
+        <v>474569</v>
       </c>
       <c r="R2" t="n">
-        <v>6670955</v>
+        <v>6670992</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120893178</v>
+        <v>120896971</v>
       </c>
       <c r="B3" t="n">
-        <v>95704</v>
+        <v>98159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474738</v>
+        <v>474968</v>
       </c>
       <c r="R3" t="n">
-        <v>6670733</v>
+        <v>6670949</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120896402</v>
+        <v>120894059</v>
       </c>
       <c r="B4" t="n">
-        <v>92037</v>
+        <v>90763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +925,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474978</v>
+        <v>474698</v>
       </c>
       <c r="R4" t="n">
-        <v>6670823</v>
+        <v>6671085</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120896971</v>
+        <v>120896402</v>
       </c>
       <c r="B5" t="n">
-        <v>98157</v>
+        <v>92039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1037,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,24 +1065,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474968</v>
+        <v>474978</v>
       </c>
       <c r="R5" t="n">
-        <v>6670949</v>
+        <v>6670823</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120895528</v>
+        <v>120893178</v>
       </c>
       <c r="B6" t="n">
-        <v>95704</v>
+        <v>95706</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474569</v>
+        <v>474738</v>
       </c>
       <c r="R6" t="n">
-        <v>6670992</v>
+        <v>6670733</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120896288</v>
+        <v>120893848</v>
       </c>
       <c r="B7" t="n">
-        <v>98157</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,52 +1270,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474950</v>
+        <v>474727</v>
       </c>
       <c r="R7" t="n">
-        <v>6670755</v>
+        <v>6670955</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120894059</v>
+        <v>120896288</v>
       </c>
       <c r="B8" t="n">
-        <v>90761</v>
+        <v>98159</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,38 +1382,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474698</v>
+        <v>474950</v>
       </c>
       <c r="R8" t="n">
-        <v>6671085</v>
+        <v>6670755</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120895528</v>
+        <v>120894059</v>
       </c>
       <c r="B2" t="n">
-        <v>95706</v>
+        <v>90763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474569</v>
+        <v>474698</v>
       </c>
       <c r="R2" t="n">
-        <v>6670992</v>
+        <v>6671085</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120896971</v>
+        <v>120893848</v>
       </c>
       <c r="B3" t="n">
-        <v>98159</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474968</v>
+        <v>474727</v>
       </c>
       <c r="R3" t="n">
-        <v>6670949</v>
+        <v>6670955</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120894059</v>
+        <v>120896971</v>
       </c>
       <c r="B4" t="n">
-        <v>90763</v>
+        <v>98159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +911,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474698</v>
+        <v>474968</v>
       </c>
       <c r="R4" t="n">
-        <v>6671085</v>
+        <v>6670949</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120896402</v>
+        <v>120896288</v>
       </c>
       <c r="B5" t="n">
-        <v>92039</v>
+        <v>98159</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,35 +1037,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474978</v>
+        <v>474950</v>
       </c>
       <c r="R5" t="n">
-        <v>6670823</v>
+        <v>6670755</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1258,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120893848</v>
+        <v>120895528</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>95706</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474727</v>
+        <v>474569</v>
       </c>
       <c r="R7" t="n">
-        <v>6670955</v>
+        <v>6670992</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120896288</v>
+        <v>120896402</v>
       </c>
       <c r="B8" t="n">
-        <v>98159</v>
+        <v>92039</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,40 +1387,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474950</v>
+        <v>474978</v>
       </c>
       <c r="R8" t="n">
-        <v>6670755</v>
+        <v>6670823</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120896971</v>
+        <v>120896288</v>
       </c>
       <c r="B2" t="n">
         <v>98175</v>
@@ -710,29 +710,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474968</v>
+        <v>474950</v>
       </c>
       <c r="R2" t="n">
-        <v>6670949</v>
+        <v>6670755</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120894059</v>
+        <v>120896402</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>92055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +925,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474698</v>
+        <v>474978</v>
       </c>
       <c r="R4" t="n">
-        <v>6671085</v>
+        <v>6670823</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120895528</v>
+        <v>120896971</v>
       </c>
       <c r="B6" t="n">
-        <v>95722</v>
+        <v>98175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1158,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474569</v>
+        <v>474968</v>
       </c>
       <c r="R6" t="n">
-        <v>6670992</v>
+        <v>6670949</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120896402</v>
+        <v>120894059</v>
       </c>
       <c r="B7" t="n">
-        <v>92055</v>
+        <v>90779</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,47 +1284,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474978</v>
+        <v>474698</v>
       </c>
       <c r="R7" t="n">
-        <v>6670823</v>
+        <v>6671085</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120896288</v>
+        <v>120895528</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>95722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,52 +1396,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474950</v>
+        <v>474569</v>
       </c>
       <c r="R8" t="n">
-        <v>6670755</v>
+        <v>6670992</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120896288</v>
+        <v>120894059</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474950</v>
+        <v>474698</v>
       </c>
       <c r="R2" t="n">
-        <v>6670755</v>
+        <v>6671085</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120893178</v>
+        <v>120895528</v>
       </c>
       <c r="B3" t="n">
-        <v>95722</v>
+        <v>95732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474738</v>
+        <v>474569</v>
       </c>
       <c r="R3" t="n">
-        <v>6670733</v>
+        <v>6670992</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +902,7 @@
         <v>120896402</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,7 +1023,7 @@
         <v>120893848</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1149,7 +1135,7 @@
         <v>120896971</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1272,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120894059</v>
+        <v>120896288</v>
       </c>
       <c r="B7" t="n">
-        <v>90779</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,38 +1270,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474698</v>
+        <v>474950</v>
       </c>
       <c r="R7" t="n">
-        <v>6671085</v>
+        <v>6670755</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120895528</v>
+        <v>120893178</v>
       </c>
       <c r="B8" t="n">
-        <v>95722</v>
+        <v>95732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474569</v>
+        <v>474738</v>
       </c>
       <c r="R8" t="n">
-        <v>6670992</v>
+        <v>6670733</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120896402</v>
+        <v>120896971</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,19 +939,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474978</v>
+        <v>474968</v>
       </c>
       <c r="R4" t="n">
-        <v>6670823</v>
+        <v>6670949</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1132,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120896971</v>
+        <v>120896402</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>92065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1172,24 +1177,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474968</v>
+        <v>474978</v>
       </c>
       <c r="R6" t="n">
-        <v>6670949</v>
+        <v>6670823</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120896288</v>
+        <v>120893178</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>95732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,52 +1270,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474950</v>
+        <v>474738</v>
       </c>
       <c r="R7" t="n">
-        <v>6670755</v>
+        <v>6670733</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120893178</v>
+        <v>120896288</v>
       </c>
       <c r="B8" t="n">
-        <v>95732</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,38 +1382,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474738</v>
+        <v>474950</v>
       </c>
       <c r="R8" t="n">
-        <v>6670733</v>
+        <v>6670755</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 53053-2024 artfynd.xlsx
+++ b/artfynd/A 53053-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120894059</v>
+        <v>120896402</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>92077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
+          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474698</v>
+        <v>474978</v>
       </c>
       <c r="R2" t="n">
-        <v>6671085</v>
+        <v>6670823</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120895528</v>
+        <v>120893178</v>
       </c>
       <c r="B3" t="n">
-        <v>95732</v>
+        <v>95744</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474569</v>
+        <v>474738</v>
       </c>
       <c r="R3" t="n">
-        <v>6670992</v>
+        <v>6670733</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120896971</v>
+        <v>120895528</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>95744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,52 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474968</v>
+        <v>474569</v>
       </c>
       <c r="R4" t="n">
-        <v>6670949</v>
+        <v>6670992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120893848</v>
+        <v>120896971</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1032,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474727</v>
+        <v>474968</v>
       </c>
       <c r="R5" t="n">
-        <v>6670955</v>
+        <v>6670949</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120896402</v>
+        <v>120894059</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>90801</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,47 +1158,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Låsen, Lilla Låsen, Dlr</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474978</v>
+        <v>474698</v>
       </c>
       <c r="R6" t="n">
-        <v>6670823</v>
+        <v>6671085</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120893178</v>
+        <v>120893848</v>
       </c>
       <c r="B7" t="n">
-        <v>95732</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474738</v>
+        <v>474727</v>
       </c>
       <c r="R7" t="n">
-        <v>6670733</v>
+        <v>6670955</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,7 +1373,7 @@
         <v>120896288</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
